--- a/Nao-Conformidade/RNC-modelo.xlsx
+++ b/Nao-Conformidade/RNC-modelo.xlsx
@@ -315,7 +315,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">A verificação deve ser feita por quem não executou as ações.</t>
+          <t xml:space="preserve">Convém que a verificação seja feita por quem não executou as ações. É uma convenção deste material.</t>
         </r>
       </text>
     </comment>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">O indicador, a meta e o período de observação foram definidos antes da implantação.</t>
   </si>
   <si>
-    <t xml:space="preserve">A eficácia foi verificada por quem não executou as ações.</t>
+    <t xml:space="preserve">A eficácia foi verificada, de preferência por quem não executou as ações.</t>
   </si>
   <si>
     <t xml:space="preserve">Os riscos, os procedimentos e os treinamentos foram atualizados.</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">Registro do pedido</t>
   </si>
   <si>
-    <t xml:space="preserve">Atendente do turno do almoço, auditor líder</t>
+    <t xml:space="preserve">Atendente do turno da tarde, auditor líder</t>
   </si>
   <si>
     <t xml:space="preserve">Atendente líder</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">Por que o roteiro não traz a pergunta?</t>
   </si>
   <si>
-    <t xml:space="preserve">O roteiro foi escrito antes da revisão 2 da instrução, de julho de 2026, e não foi atualizado.</t>
+    <t xml:space="preserve">O roteiro foi escrito antes da revisão 2 da instrução, de setembro de 2026, e não foi atualizado.</t>
   </si>
   <si>
     <t xml:space="preserve">Comparação das datas dos dois documentos.</t>
@@ -2045,11 +2045,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="43356309"/>
-        <c:axId val="53438698"/>
+        <c:axId val="49742610"/>
+        <c:axId val="43803319"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="43356309"/>
+        <c:axId val="49742610"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2081,7 +2081,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53438698"/>
+        <c:crossAx val="43803319"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2089,7 +2089,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53438698"/>
+        <c:axId val="43803319"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2129,7 +2129,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43356309"/>
+        <c:crossAx val="49742610"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2399,11 +2399,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="40821045"/>
-        <c:axId val="48239738"/>
+        <c:axId val="52858793"/>
+        <c:axId val="50596471"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40821045"/>
+        <c:axId val="52858793"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2435,7 +2435,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48239738"/>
+        <c:crossAx val="50596471"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2443,7 +2443,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48239738"/>
+        <c:axId val="50596471"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2483,7 +2483,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40821045"/>
+        <c:crossAx val="52858793"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2800,11 +2800,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="18148954"/>
-        <c:axId val="56188517"/>
+        <c:axId val="10075038"/>
+        <c:axId val="80335472"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="18148954"/>
+        <c:axId val="10075038"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2836,7 +2836,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56188517"/>
+        <c:crossAx val="80335472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2844,7 +2844,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56188517"/>
+        <c:axId val="80335472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2884,7 +2884,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18148954"/>
+        <c:crossAx val="10075038"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3225,11 +3225,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="74473483"/>
-        <c:axId val="49560026"/>
+        <c:axId val="10653689"/>
+        <c:axId val="79556181"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74473483"/>
+        <c:axId val="10653689"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3261,7 +3261,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49560026"/>
+        <c:crossAx val="79556181"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3269,7 +3269,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49560026"/>
+        <c:axId val="79556181"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3309,7 +3309,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74473483"/>
+        <c:crossAx val="10653689"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6812,6 +6812,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L6" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Menor é melhor: falhas, atrasos. Maior é melhor: entregas no prazo." promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D6" type="list">
       <formula1>"Menor é melhor,Maior é melhor"</formula1>
       <formula2>0</formula2>
@@ -6826,10 +6830,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="A mesma não conformidade ocorreu de novo depois das ações?" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G7" type="list">
       <formula1>"Sim,Não"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L6" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Antes, Durante ou Depois das ações" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D11:D22" type="list">
